--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B4" t="n">
-        <v>103803</v>
+        <v>101522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R4" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B5" t="n">
-        <v>101447</v>
+        <v>103878</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R5" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>127157000</v>
       </c>
       <c r="B7" t="n">
-        <v>79351</v>
+        <v>79382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127156619</v>
+        <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>105308</v>
+        <v>101522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724500</v>
+        <v>724605</v>
       </c>
       <c r="R8" t="n">
-        <v>6645668</v>
+        <v>6645716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127157449</v>
+        <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>101447</v>
+        <v>105383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724605</v>
+        <v>724500</v>
       </c>
       <c r="R9" t="n">
-        <v>6645716</v>
+        <v>6645668</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105308</v>
+        <v>105383</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101447</v>
+        <v>101522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127157120</v>
+        <v>127157276</v>
       </c>
       <c r="B14" t="n">
-        <v>100543</v>
+        <v>98458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724542</v>
+        <v>724549</v>
       </c>
       <c r="R14" t="n">
-        <v>6645741</v>
+        <v>6645754</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127157276</v>
+        <v>127157120</v>
       </c>
       <c r="B15" t="n">
-        <v>98383</v>
+        <v>100618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724549</v>
+        <v>724542</v>
       </c>
       <c r="R15" t="n">
-        <v>6645754</v>
+        <v>6645741</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
         <v>127156732</v>
       </c>
       <c r="B16" t="n">
-        <v>101447</v>
+        <v>101522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127157323</v>
       </c>
       <c r="B17" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100450</v>
+        <v>100525</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>127156885</v>
       </c>
       <c r="B4" t="n">
-        <v>101522</v>
+        <v>101528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>127157198</v>
       </c>
       <c r="B5" t="n">
-        <v>103878</v>
+        <v>103884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>127157000</v>
       </c>
       <c r="B7" t="n">
-        <v>79382</v>
+        <v>79385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>101522</v>
+        <v>101528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>105383</v>
+        <v>105389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105383</v>
+        <v>105389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101522</v>
+        <v>101528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127157276</v>
       </c>
       <c r="B14" t="n">
-        <v>98458</v>
+        <v>98464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127157120</v>
       </c>
       <c r="B15" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127156732</v>
       </c>
       <c r="B16" t="n">
-        <v>101522</v>
+        <v>101528</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127157323</v>
       </c>
       <c r="B17" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100525</v>
+        <v>100531</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B4" t="n">
-        <v>101528</v>
+        <v>103884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R4" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B5" t="n">
-        <v>103884</v>
+        <v>101528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R5" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127157276</v>
+        <v>127157120</v>
       </c>
       <c r="B14" t="n">
-        <v>98464</v>
+        <v>100624</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724549</v>
+        <v>724542</v>
       </c>
       <c r="R14" t="n">
-        <v>6645754</v>
+        <v>6645741</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127157120</v>
+        <v>127157276</v>
       </c>
       <c r="B15" t="n">
-        <v>100624</v>
+        <v>98464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724542</v>
+        <v>724549</v>
       </c>
       <c r="R15" t="n">
-        <v>6645741</v>
+        <v>6645754</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B4" t="n">
-        <v>103884</v>
+        <v>101529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R4" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B5" t="n">
-        <v>101528</v>
+        <v>103885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R5" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127157449</v>
+        <v>127156619</v>
       </c>
       <c r="B8" t="n">
-        <v>101528</v>
+        <v>105390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>221141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724605</v>
+        <v>724500</v>
       </c>
       <c r="R8" t="n">
-        <v>6645716</v>
+        <v>6645668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127156619</v>
+        <v>127157449</v>
       </c>
       <c r="B9" t="n">
-        <v>105389</v>
+        <v>101529</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724500</v>
+        <v>724605</v>
       </c>
       <c r="R9" t="n">
-        <v>6645668</v>
+        <v>6645716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105389</v>
+        <v>105390</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101528</v>
+        <v>101529</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127157120</v>
+        <v>127157276</v>
       </c>
       <c r="B14" t="n">
-        <v>100624</v>
+        <v>98465</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724542</v>
+        <v>724549</v>
       </c>
       <c r="R14" t="n">
-        <v>6645741</v>
+        <v>6645754</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127157276</v>
+        <v>127157120</v>
       </c>
       <c r="B15" t="n">
-        <v>98464</v>
+        <v>100625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724549</v>
+        <v>724542</v>
       </c>
       <c r="R15" t="n">
-        <v>6645754</v>
+        <v>6645741</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127156732</v>
+        <v>127157323</v>
       </c>
       <c r="B16" t="n">
-        <v>101528</v>
+        <v>100625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724500</v>
+        <v>724570</v>
       </c>
       <c r="R16" t="n">
-        <v>6645668</v>
+        <v>6645756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127157323</v>
+        <v>127156732</v>
       </c>
       <c r="B17" t="n">
-        <v>100624</v>
+        <v>101529</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724570</v>
+        <v>724500</v>
       </c>
       <c r="R17" t="n">
-        <v>6645756</v>
+        <v>6645668</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127157323</v>
+        <v>127156732</v>
       </c>
       <c r="B16" t="n">
-        <v>100625</v>
+        <v>101529</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724570</v>
+        <v>724500</v>
       </c>
       <c r="R16" t="n">
-        <v>6645756</v>
+        <v>6645668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127156732</v>
+        <v>127157323</v>
       </c>
       <c r="B17" t="n">
-        <v>101529</v>
+        <v>100625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724500</v>
+        <v>724570</v>
       </c>
       <c r="R17" t="n">
-        <v>6645668</v>
+        <v>6645756</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127156619</v>
+        <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>105390</v>
+        <v>101529</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724500</v>
+        <v>724605</v>
       </c>
       <c r="R8" t="n">
-        <v>6645668</v>
+        <v>6645716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127157449</v>
+        <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>101529</v>
+        <v>105390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724605</v>
+        <v>724500</v>
       </c>
       <c r="R9" t="n">
-        <v>6645716</v>
+        <v>6645668</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127156732</v>
+        <v>127157323</v>
       </c>
       <c r="B16" t="n">
-        <v>101529</v>
+        <v>100625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724500</v>
+        <v>724570</v>
       </c>
       <c r="R16" t="n">
-        <v>6645668</v>
+        <v>6645756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127157323</v>
+        <v>127156732</v>
       </c>
       <c r="B17" t="n">
-        <v>100625</v>
+        <v>101529</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724570</v>
+        <v>724500</v>
       </c>
       <c r="R17" t="n">
-        <v>6645756</v>
+        <v>6645668</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B4" t="n">
-        <v>101529</v>
+        <v>103891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R4" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B5" t="n">
-        <v>103885</v>
+        <v>101533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R5" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>127157000</v>
       </c>
       <c r="B7" t="n">
-        <v>79385</v>
+        <v>79389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>101529</v>
+        <v>101533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>105390</v>
+        <v>105396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105390</v>
+        <v>105396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101529</v>
+        <v>101533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127157276</v>
+        <v>127157120</v>
       </c>
       <c r="B14" t="n">
-        <v>98465</v>
+        <v>100629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724549</v>
+        <v>724542</v>
       </c>
       <c r="R14" t="n">
-        <v>6645754</v>
+        <v>6645741</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127157120</v>
+        <v>127157276</v>
       </c>
       <c r="B15" t="n">
-        <v>100625</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724542</v>
+        <v>724549</v>
       </c>
       <c r="R15" t="n">
-        <v>6645741</v>
+        <v>6645754</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
         <v>127156732</v>
       </c>
       <c r="B16" t="n">
-        <v>101529</v>
+        <v>101533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127157323</v>
       </c>
       <c r="B17" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B4" t="n">
-        <v>103891</v>
+        <v>101533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R4" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B5" t="n">
-        <v>101533</v>
+        <v>103891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R5" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127157120</v>
+        <v>127157276</v>
       </c>
       <c r="B14" t="n">
-        <v>100629</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724542</v>
+        <v>724549</v>
       </c>
       <c r="R14" t="n">
-        <v>6645741</v>
+        <v>6645754</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127157276</v>
+        <v>127157120</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>100629</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724549</v>
+        <v>724542</v>
       </c>
       <c r="R15" t="n">
-        <v>6645754</v>
+        <v>6645741</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B4" t="n">
-        <v>101533</v>
+        <v>103893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R4" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B5" t="n">
-        <v>103891</v>
+        <v>101534</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R5" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>101533</v>
+        <v>101534</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>105396</v>
+        <v>105398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105396</v>
+        <v>105398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101533</v>
+        <v>101534</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127157276</v>
+        <v>127157120</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>100630</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724549</v>
+        <v>724542</v>
       </c>
       <c r="R14" t="n">
-        <v>6645754</v>
+        <v>6645741</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127157120</v>
+        <v>127157276</v>
       </c>
       <c r="B15" t="n">
-        <v>100629</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724542</v>
+        <v>724549</v>
       </c>
       <c r="R15" t="n">
-        <v>6645741</v>
+        <v>6645754</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127156732</v>
+        <v>127157323</v>
       </c>
       <c r="B16" t="n">
-        <v>101533</v>
+        <v>100630</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724500</v>
+        <v>724570</v>
       </c>
       <c r="R16" t="n">
-        <v>6645668</v>
+        <v>6645756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127157323</v>
+        <v>127156732</v>
       </c>
       <c r="B17" t="n">
-        <v>100629</v>
+        <v>101534</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724570</v>
+        <v>724500</v>
       </c>
       <c r="R17" t="n">
-        <v>6645756</v>
+        <v>6645668</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B4" t="n">
-        <v>103893</v>
+        <v>101536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R4" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B5" t="n">
-        <v>101534</v>
+        <v>103895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R5" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>127157000</v>
       </c>
       <c r="B7" t="n">
-        <v>79389</v>
+        <v>79391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>105398</v>
+        <v>105400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105398</v>
+        <v>105400</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127157120</v>
+        <v>127157276</v>
       </c>
       <c r="B14" t="n">
-        <v>100630</v>
+        <v>98472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724542</v>
+        <v>724549</v>
       </c>
       <c r="R14" t="n">
-        <v>6645741</v>
+        <v>6645754</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127157276</v>
+        <v>127157120</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>100632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724549</v>
+        <v>724542</v>
       </c>
       <c r="R15" t="n">
-        <v>6645754</v>
+        <v>6645741</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127157323</v>
+        <v>127156732</v>
       </c>
       <c r="B16" t="n">
-        <v>100630</v>
+        <v>101536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724570</v>
+        <v>724500</v>
       </c>
       <c r="R16" t="n">
-        <v>6645756</v>
+        <v>6645668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127156732</v>
+        <v>127157323</v>
       </c>
       <c r="B17" t="n">
-        <v>101534</v>
+        <v>100632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724500</v>
+        <v>724570</v>
       </c>
       <c r="R17" t="n">
-        <v>6645668</v>
+        <v>6645756</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B4" t="n">
-        <v>101536</v>
+        <v>103895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R4" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B5" t="n">
-        <v>103895</v>
+        <v>101536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R5" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127157449</v>
+        <v>127156619</v>
       </c>
       <c r="B8" t="n">
-        <v>101536</v>
+        <v>105400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>221141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724605</v>
+        <v>724500</v>
       </c>
       <c r="R8" t="n">
-        <v>6645716</v>
+        <v>6645668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127156619</v>
+        <v>127157449</v>
       </c>
       <c r="B9" t="n">
-        <v>105400</v>
+        <v>101536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724500</v>
+        <v>724605</v>
       </c>
       <c r="R9" t="n">
-        <v>6645668</v>
+        <v>6645716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127156732</v>
+        <v>127157323</v>
       </c>
       <c r="B16" t="n">
-        <v>101536</v>
+        <v>100632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724500</v>
+        <v>724570</v>
       </c>
       <c r="R16" t="n">
-        <v>6645668</v>
+        <v>6645756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127157323</v>
+        <v>127156732</v>
       </c>
       <c r="B17" t="n">
-        <v>100632</v>
+        <v>101536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724570</v>
+        <v>724500</v>
       </c>
       <c r="R17" t="n">
-        <v>6645756</v>
+        <v>6645668</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B4" t="n">
-        <v>103895</v>
+        <v>101536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R4" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B5" t="n">
-        <v>101536</v>
+        <v>103895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R5" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127156619</v>
+        <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>105400</v>
+        <v>101536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724500</v>
+        <v>724605</v>
       </c>
       <c r="R8" t="n">
-        <v>6645668</v>
+        <v>6645716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127157449</v>
+        <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>101536</v>
+        <v>105400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724605</v>
+        <v>724500</v>
       </c>
       <c r="R9" t="n">
-        <v>6645716</v>
+        <v>6645668</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127157276</v>
+        <v>127157120</v>
       </c>
       <c r="B14" t="n">
-        <v>98472</v>
+        <v>100632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724549</v>
+        <v>724542</v>
       </c>
       <c r="R14" t="n">
-        <v>6645754</v>
+        <v>6645741</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127157120</v>
+        <v>127157276</v>
       </c>
       <c r="B15" t="n">
-        <v>100632</v>
+        <v>98472</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724542</v>
+        <v>724549</v>
       </c>
       <c r="R15" t="n">
-        <v>6645741</v>
+        <v>6645754</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127157323</v>
+        <v>127156732</v>
       </c>
       <c r="B16" t="n">
-        <v>100632</v>
+        <v>101536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724570</v>
+        <v>724500</v>
       </c>
       <c r="R16" t="n">
-        <v>6645756</v>
+        <v>6645668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127156732</v>
+        <v>127157323</v>
       </c>
       <c r="B17" t="n">
-        <v>101536</v>
+        <v>100632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724500</v>
+        <v>724570</v>
       </c>
       <c r="R17" t="n">
-        <v>6645668</v>
+        <v>6645756</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>127156885</v>
       </c>
       <c r="B4" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>127157198</v>
       </c>
       <c r="B5" t="n">
-        <v>103895</v>
+        <v>103901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>105400</v>
+        <v>105406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105400</v>
+        <v>105406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127157120</v>
       </c>
       <c r="B14" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127157276</v>
       </c>
       <c r="B15" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127156732</v>
       </c>
       <c r="B16" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127157323</v>
       </c>
       <c r="B17" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>127156885</v>
       </c>
       <c r="B4" t="n">
-        <v>101542</v>
+        <v>101545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>127157198</v>
       </c>
       <c r="B5" t="n">
-        <v>103901</v>
+        <v>103904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>127157000</v>
       </c>
       <c r="B7" t="n">
-        <v>79391</v>
+        <v>79394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>101542</v>
+        <v>101545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101542</v>
+        <v>101545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127157120</v>
+        <v>127157276</v>
       </c>
       <c r="B14" t="n">
-        <v>100638</v>
+        <v>98481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724542</v>
+        <v>724549</v>
       </c>
       <c r="R14" t="n">
-        <v>6645741</v>
+        <v>6645754</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127157276</v>
+        <v>127157120</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>100641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724549</v>
+        <v>724542</v>
       </c>
       <c r="R15" t="n">
-        <v>6645754</v>
+        <v>6645741</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
         <v>127156732</v>
       </c>
       <c r="B16" t="n">
-        <v>101542</v>
+        <v>101545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127157323</v>
       </c>
       <c r="B17" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>127156885</v>
       </c>
       <c r="B4" t="n">
-        <v>101545</v>
+        <v>101553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>127157198</v>
       </c>
       <c r="B5" t="n">
-        <v>103904</v>
+        <v>103912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>127157000</v>
       </c>
       <c r="B7" t="n">
-        <v>79394</v>
+        <v>79400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>101545</v>
+        <v>101553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101545</v>
+        <v>101553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127157276</v>
       </c>
       <c r="B14" t="n">
-        <v>98481</v>
+        <v>98489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127157120</v>
       </c>
       <c r="B15" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127156732</v>
+        <v>127157323</v>
       </c>
       <c r="B16" t="n">
-        <v>101545</v>
+        <v>100649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724500</v>
+        <v>724570</v>
       </c>
       <c r="R16" t="n">
-        <v>6645668</v>
+        <v>6645756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127157323</v>
+        <v>127156732</v>
       </c>
       <c r="B17" t="n">
-        <v>100641</v>
+        <v>101553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724570</v>
+        <v>724500</v>
       </c>
       <c r="R17" t="n">
-        <v>6645756</v>
+        <v>6645668</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B4" t="n">
-        <v>101553</v>
+        <v>103913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R4" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B5" t="n">
-        <v>103912</v>
+        <v>101554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R5" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>101553</v>
+        <v>101554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101553</v>
+        <v>101554</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127157276</v>
       </c>
       <c r="B14" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127157120</v>
       </c>
       <c r="B15" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127157323</v>
+        <v>127156732</v>
       </c>
       <c r="B16" t="n">
-        <v>100649</v>
+        <v>101554</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724570</v>
+        <v>724500</v>
       </c>
       <c r="R16" t="n">
-        <v>6645756</v>
+        <v>6645668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127156732</v>
+        <v>127157323</v>
       </c>
       <c r="B17" t="n">
-        <v>101553</v>
+        <v>100650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724500</v>
+        <v>724570</v>
       </c>
       <c r="R17" t="n">
-        <v>6645668</v>
+        <v>6645756</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B4" t="n">
-        <v>103913</v>
+        <v>101522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R4" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B5" t="n">
-        <v>101554</v>
+        <v>103878</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R5" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100650</v>
+        <v>100618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>127157000</v>
       </c>
       <c r="B7" t="n">
-        <v>79400</v>
+        <v>79382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>101554</v>
+        <v>101522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>105418</v>
+        <v>105383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100650</v>
+        <v>100618</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105418</v>
+        <v>105383</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100650</v>
+        <v>100618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101554</v>
+        <v>101522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127157276</v>
       </c>
       <c r="B14" t="n">
-        <v>98490</v>
+        <v>98458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127157120</v>
       </c>
       <c r="B15" t="n">
-        <v>100650</v>
+        <v>100618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127156732</v>
       </c>
       <c r="B16" t="n">
-        <v>101554</v>
+        <v>101522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127157323</v>
       </c>
       <c r="B17" t="n">
-        <v>100650</v>
+        <v>100618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98385</v>
+        <v>98353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100557</v>
+        <v>100525</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127156885</v>
+        <v>127157198</v>
       </c>
       <c r="B4" t="n">
-        <v>101522</v>
+        <v>103913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724534</v>
+        <v>724542</v>
       </c>
       <c r="R4" t="n">
-        <v>6645685</v>
+        <v>6645741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127157198</v>
+        <v>127156885</v>
       </c>
       <c r="B5" t="n">
-        <v>103878</v>
+        <v>101554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724542</v>
+        <v>724534</v>
       </c>
       <c r="R5" t="n">
-        <v>6645741</v>
+        <v>6645685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>127156873</v>
       </c>
       <c r="B6" t="n">
-        <v>100618</v>
+        <v>100650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>127157000</v>
       </c>
       <c r="B7" t="n">
-        <v>79382</v>
+        <v>79400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>127157449</v>
       </c>
       <c r="B8" t="n">
-        <v>101522</v>
+        <v>101554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>127156619</v>
       </c>
       <c r="B9" t="n">
-        <v>105383</v>
+        <v>105418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127156623</v>
       </c>
       <c r="B10" t="n">
-        <v>100618</v>
+        <v>100650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105383</v>
+        <v>105418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127157427</v>
       </c>
       <c r="B12" t="n">
-        <v>100618</v>
+        <v>100650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>127157320</v>
       </c>
       <c r="B13" t="n">
-        <v>101522</v>
+        <v>101554</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127157276</v>
       </c>
       <c r="B14" t="n">
-        <v>98458</v>
+        <v>98490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127157120</v>
       </c>
       <c r="B15" t="n">
-        <v>100618</v>
+        <v>100650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127156732</v>
       </c>
       <c r="B16" t="n">
-        <v>101522</v>
+        <v>101554</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127157323</v>
       </c>
       <c r="B17" t="n">
-        <v>100618</v>
+        <v>100650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>127157363</v>
       </c>
       <c r="B18" t="n">
-        <v>98353</v>
+        <v>98385</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>127157212</v>
       </c>
       <c r="B19" t="n">
-        <v>100525</v>
+        <v>100557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>69478687</v>
       </c>
       <c r="B2" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724693.6873071031</v>
+        <v>724694</v>
       </c>
       <c r="R2" t="n">
-        <v>6646089.390687955</v>
+        <v>6646089</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2000-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>69718341</v>
       </c>
       <c r="B3" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724875.9254718424</v>
+        <v>724876</v>
       </c>
       <c r="R3" t="n">
-        <v>6645412.67291071</v>
+        <v>6645413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +854,9 @@
           <t>1998-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1998-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69478687</v>
       </c>
       <c r="B2" t="n">
-        <v>99057</v>
+        <v>99058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>69718341</v>
       </c>
       <c r="B3" t="n">
-        <v>109784</v>
+        <v>109779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69478687</v>
       </c>
       <c r="B2" t="n">
-        <v>99058</v>
+        <v>99059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>69718341</v>
       </c>
       <c r="B3" t="n">
-        <v>109779</v>
+        <v>109780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69478687</v>
       </c>
       <c r="B2" t="n">
-        <v>99059</v>
+        <v>99062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>69718341</v>
       </c>
       <c r="B3" t="n">
-        <v>109780</v>
+        <v>109778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>69718341</v>
       </c>
       <c r="B3" t="n">
-        <v>109778</v>
+        <v>109779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69478687</v>
       </c>
       <c r="B2" t="n">
-        <v>99062</v>
+        <v>99061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69478687</v>
       </c>
       <c r="B2" t="n">
-        <v>99061</v>
+        <v>99067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>69718341</v>
       </c>
       <c r="B3" t="n">
-        <v>109779</v>
+        <v>109785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69478687</v>
       </c>
       <c r="B2" t="n">
-        <v>99067</v>
+        <v>99070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>69718341</v>
       </c>
       <c r="B3" t="n">
-        <v>109785</v>
+        <v>109792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69478687</v>
       </c>
       <c r="B2" t="n">
-        <v>99070</v>
+        <v>99075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>69718341</v>
       </c>
       <c r="B3" t="n">
-        <v>109792</v>
+        <v>109797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69478687</v>
       </c>
       <c r="B2" t="n">
-        <v>99075</v>
+        <v>99077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>69718341</v>
       </c>
       <c r="B3" t="n">
-        <v>109797</v>
+        <v>109800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69478687</v>
+        <v>127157000</v>
       </c>
       <c r="B2" t="n">
-        <v>99077</v>
+        <v>79699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>6430</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>400 m O om Utanå, Upl</t>
+          <t>Ytterstycket, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724694</v>
+        <v>724534</v>
       </c>
       <c r="R2" t="n">
-        <v>6646089</v>
+        <v>6645685</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,70 +756,61 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lund</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69718341</v>
+        <v>127157780</v>
       </c>
       <c r="B3" t="n">
-        <v>109800</v>
+        <v>79699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220228</v>
+        <v>6430</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>40 m V om torpet Strömmen, Upl</t>
+          <t>Ytterstycket, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724876</v>
+        <v>724472</v>
       </c>
       <c r="R3" t="n">
-        <v>6645413</v>
+        <v>6645824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1998-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>6 blomstänglar och ca 20 bladrosetter</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,35 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>I gräsvegetation på kanten av en gammal traktorväg</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127157198</v>
+        <v>127157363</v>
       </c>
       <c r="B4" t="n">
-        <v>103913</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724542</v>
+        <v>724582</v>
       </c>
       <c r="R4" t="n">
-        <v>6645741</v>
+        <v>6645761</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127156885</v>
+        <v>127157657</v>
       </c>
       <c r="B5" t="n">
-        <v>101554</v>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724534</v>
+        <v>724479</v>
       </c>
       <c r="R5" t="n">
-        <v>6645685</v>
+        <v>6645800</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127156873</v>
+        <v>69478687</v>
       </c>
       <c r="B6" t="n">
-        <v>100650</v>
+        <v>99218</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>400 m O om Utanå, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>724534</v>
+        <v>724694</v>
       </c>
       <c r="R6" t="n">
-        <v>6645685</v>
+        <v>6646089</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,12 +1128,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2000-12-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1172,26 +1149,35 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127157000</v>
+        <v>127157276</v>
       </c>
       <c r="B7" t="n">
-        <v>79400</v>
+        <v>99141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6430</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slät lönnlav</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bacidia fraxinea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lönnr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724534</v>
+        <v>724549</v>
       </c>
       <c r="R7" t="n">
-        <v>6645685</v>
+        <v>6645754</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,45 +1271,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127157449</v>
+        <v>69718341</v>
       </c>
       <c r="B8" t="n">
-        <v>101554</v>
+        <v>109947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>40 m V om torpet Strömmen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724605</v>
+        <v>724876</v>
       </c>
       <c r="R8" t="n">
-        <v>6645716</v>
+        <v>6645413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,12 +1336,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>1998-12-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>6 blomstänglar och ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1366,26 +1357,35 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>I gräsvegetation på kanten av en gammal traktorväg</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127156619</v>
+        <v>69478692</v>
       </c>
       <c r="B9" t="n">
-        <v>105418</v>
+        <v>104880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,37 +1393,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>220460</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Cardamine bulbifera</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnalnäset, Utanå, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724500</v>
+        <v>724694</v>
       </c>
       <c r="R9" t="n">
-        <v>6645668</v>
+        <v>6646089</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1447,12 +1447,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2000-12-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1463,26 +1468,35 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127156623</v>
+        <v>127156619</v>
       </c>
       <c r="B10" t="n">
-        <v>100650</v>
+        <v>106156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1490,21 +1504,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1579,7 +1593,7 @@
         <v>127157474</v>
       </c>
       <c r="B11" t="n">
-        <v>105418</v>
+        <v>106156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1687,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127157427</v>
+        <v>127157730</v>
       </c>
       <c r="B12" t="n">
-        <v>100650</v>
+        <v>106156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1698,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1722,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724605</v>
+        <v>724476</v>
       </c>
       <c r="R12" t="n">
-        <v>6645716</v>
+        <v>6645815</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,14 +1784,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127157320</v>
+        <v>127156732</v>
       </c>
       <c r="B13" t="n">
-        <v>101554</v>
+        <v>102241</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1805,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>724570</v>
+        <v>724500</v>
       </c>
       <c r="R13" t="n">
-        <v>6645756</v>
+        <v>6645668</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,32 +1881,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127157276</v>
+        <v>127156885</v>
       </c>
       <c r="B14" t="n">
-        <v>98490</v>
+        <v>102241</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219862</v>
+        <v>221235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1916,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724549</v>
+        <v>724534</v>
       </c>
       <c r="R14" t="n">
-        <v>6645754</v>
+        <v>6645685</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,32 +1978,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127157120</v>
+        <v>127157320</v>
       </c>
       <c r="B15" t="n">
-        <v>100650</v>
+        <v>102241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1999,10 +2013,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724542</v>
+        <v>724570</v>
       </c>
       <c r="R15" t="n">
-        <v>6645741</v>
+        <v>6645756</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,14 +2075,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127156732</v>
+        <v>127157449</v>
       </c>
       <c r="B16" t="n">
-        <v>101554</v>
+        <v>102241</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2096,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724500</v>
+        <v>724605</v>
       </c>
       <c r="R16" t="n">
-        <v>6645668</v>
+        <v>6645716</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127157323</v>
+        <v>127157962</v>
       </c>
       <c r="B17" t="n">
-        <v>100650</v>
+        <v>102241</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2193,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724570</v>
+        <v>724463</v>
       </c>
       <c r="R17" t="n">
-        <v>6645756</v>
+        <v>6645828</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,10 +2269,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127157363</v>
+        <v>127157198</v>
       </c>
       <c r="B18" t="n">
-        <v>98385</v>
+        <v>104628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,21 +2280,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>222412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2290,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>724582</v>
+        <v>724542</v>
       </c>
       <c r="R18" t="n">
-        <v>6645761</v>
+        <v>6645741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,10 +2366,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127157212</v>
+        <v>127157709</v>
       </c>
       <c r="B19" t="n">
-        <v>100557</v>
+        <v>104628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2363,16 +2377,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2387,10 +2401,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>724542</v>
+        <v>724476</v>
       </c>
       <c r="R19" t="n">
-        <v>6645741</v>
+        <v>6645815</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,6 +2460,782 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127156623</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>724500</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6645668</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127156873</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>724534</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6645685</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127157120</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>724542</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6645741</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127157323</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>724570</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6645756</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127157427</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>724605</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6645716</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127157668</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>724479</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6645800</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127157212</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>724542</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6645741</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127157952</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>724463</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6645828</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157780</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157363</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157657</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69478687</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157276</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69718341</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69478692</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127156619</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1684,6 +1734,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157474</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1781,6 +1836,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157730</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1878,6 +1938,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127156732</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1975,6 +2040,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127156885</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2072,6 +2142,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157320</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2169,6 +2244,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157449</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2266,6 +2346,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157962</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2363,6 +2448,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157198</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2460,6 +2550,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157709</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2557,6 +2652,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127156623</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2654,6 +2754,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127156873</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2751,6 +2856,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157120</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2848,6 +2958,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157323</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2945,6 +3060,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157427</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3042,6 +3162,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157668</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3139,6 +3264,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157212</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3236,8 +3366,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157952</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127157000</v>
+        <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>79699</v>
+        <v>96182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6430</v>
+        <v>2558</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slät lönnlav</t>
+          <t>Krushättemossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia fraxinea</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Lönnr.</t>
-        </is>
-      </c>
+          <t>Ulota crispa s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724534</v>
+        <v>724687</v>
       </c>
       <c r="R2" t="n">
-        <v>6645685</v>
+        <v>6645359</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,16 +772,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157000</t>
+          <t>https://artportalen.se/Sighting/135822036</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127157780</v>
+        <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>79699</v>
+        <v>96577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +789,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6430</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slät lönnlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia fraxinea</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lönnr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724472</v>
+        <v>724730</v>
       </c>
       <c r="R3" t="n">
-        <v>6645824</v>
+        <v>6645317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +843,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,16 +874,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157780</t>
+          <t>https://artportalen.se/Sighting/135821503</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127157363</v>
+        <v>135751450</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>96486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +891,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724582</v>
+        <v>724792</v>
       </c>
       <c r="R4" t="n">
-        <v>6645761</v>
+        <v>6645400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +945,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,16 +986,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157363</t>
+          <t>https://artportalen.se/Sighting/135751450</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127157657</v>
+        <v>135751458</v>
       </c>
       <c r="B5" t="n">
-        <v>99142</v>
+        <v>96486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +1003,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724479</v>
+        <v>724851</v>
       </c>
       <c r="R5" t="n">
-        <v>6645800</v>
+        <v>6645435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1057,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,16 +1098,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157657</t>
+          <t>https://artportalen.se/Sighting/135751458</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69478687</v>
+        <v>135751491</v>
       </c>
       <c r="B6" t="n">
-        <v>99218</v>
+        <v>96486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1115,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>400 m O om Utanå, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>724694</v>
+        <v>724851</v>
       </c>
       <c r="R6" t="n">
-        <v>6646089</v>
+        <v>6645576</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,17 +1169,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1174,40 +1195,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Lund</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69478687</t>
+          <t>https://artportalen.se/Sighting/135751491</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127157276</v>
+        <v>135751508</v>
       </c>
       <c r="B7" t="n">
-        <v>99141</v>
+        <v>96486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1227,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724549</v>
+        <v>724811</v>
       </c>
       <c r="R7" t="n">
-        <v>6645754</v>
+        <v>6645385</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,12 +1281,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,51 +1322,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157276</t>
+          <t>https://artportalen.se/Sighting/135751508</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69718341</v>
+        <v>135751448</v>
       </c>
       <c r="B8" t="n">
-        <v>109947</v>
+        <v>92105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220228</v>
+        <v>5321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>40 m V om torpet Strömmen, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724876</v>
+        <v>724792</v>
       </c>
       <c r="R8" t="n">
-        <v>6645413</v>
+        <v>6645400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,17 +1393,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1998-12-31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>6 blomstänglar och ca 20 bladrosetter</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1390,42 +1417,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>I gräsvegetation på kanten av en gammal traktorväg</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69718341</t>
+          <t>https://artportalen.se/Sighting/135751448</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69478692</v>
+        <v>135751469</v>
       </c>
       <c r="B9" t="n">
-        <v>104880</v>
+        <v>75414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,37 +1452,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220460</v>
+        <v>6427</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tandrot</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cardamine bulbifera</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Finnalnäset, Utanå, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724694</v>
+        <v>724892</v>
       </c>
       <c r="R9" t="n">
-        <v>6646089</v>
+        <v>6645469</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1487,17 +1506,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,40 +1532,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Lund</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69478692</t>
+          <t>https://artportalen.se/Sighting/135751469</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127156619</v>
+        <v>135751495</v>
       </c>
       <c r="B10" t="n">
-        <v>106156</v>
+        <v>75414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,34 +1564,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>6427</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>724500</v>
+        <v>724847</v>
       </c>
       <c r="R10" t="n">
-        <v>6645668</v>
+        <v>6645594</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,12 +1618,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,16 +1659,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127156619</t>
+          <t>https://artportalen.se/Sighting/135751495</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127157474</v>
+        <v>135820804</v>
       </c>
       <c r="B11" t="n">
-        <v>106156</v>
+        <v>75400</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,34 +1676,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>6428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>724605</v>
+        <v>724749</v>
       </c>
       <c r="R11" t="n">
-        <v>6645716</v>
+        <v>6645315</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,12 +1730,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1736,16 +1761,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157474</t>
+          <t>https://artportalen.se/Sighting/135820804</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127157730</v>
+        <v>127157000</v>
       </c>
       <c r="B12" t="n">
-        <v>106156</v>
+        <v>79699</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,21 +1778,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>6430</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724476</v>
+        <v>724534</v>
       </c>
       <c r="R12" t="n">
-        <v>6645815</v>
+        <v>6645685</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,38 +1863,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157730</t>
+          <t>https://artportalen.se/Sighting/127157000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127156732</v>
+        <v>127157780</v>
       </c>
       <c r="B13" t="n">
-        <v>102241</v>
+        <v>79699</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221235</v>
+        <v>6430</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1879,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>724500</v>
+        <v>724472</v>
       </c>
       <c r="R13" t="n">
-        <v>6645668</v>
+        <v>6645824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,51 +1965,51 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127156732</t>
+          <t>https://artportalen.se/Sighting/127157780</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127156885</v>
+        <v>135751453</v>
       </c>
       <c r="B14" t="n">
-        <v>102241</v>
+        <v>79813</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221235</v>
+        <v>6430</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724534</v>
+        <v>724795</v>
       </c>
       <c r="R14" t="n">
-        <v>6645685</v>
+        <v>6645423</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,12 +2036,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,51 +2077,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127156885</t>
+          <t>https://artportalen.se/Sighting/135751453</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127157320</v>
+        <v>135751461</v>
       </c>
       <c r="B15" t="n">
-        <v>102241</v>
+        <v>79813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221235</v>
+        <v>6430</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724570</v>
+        <v>724857</v>
       </c>
       <c r="R15" t="n">
-        <v>6645756</v>
+        <v>6645441</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,12 +2148,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2144,51 +2189,51 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157320</t>
+          <t>https://artportalen.se/Sighting/135751461</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127157449</v>
+        <v>135751463</v>
       </c>
       <c r="B16" t="n">
-        <v>102241</v>
+        <v>79813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221235</v>
+        <v>6430</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724605</v>
+        <v>724863</v>
       </c>
       <c r="R16" t="n">
-        <v>6645716</v>
+        <v>6645474</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,12 +2260,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2246,51 +2301,51 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157449</t>
+          <t>https://artportalen.se/Sighting/135751463</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127157962</v>
+        <v>135751471</v>
       </c>
       <c r="B17" t="n">
-        <v>102241</v>
+        <v>79813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>6430</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724463</v>
+        <v>724904</v>
       </c>
       <c r="R17" t="n">
-        <v>6645828</v>
+        <v>6645471</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,12 +2372,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2348,16 +2413,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157962</t>
+          <t>https://artportalen.se/Sighting/135751471</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127157198</v>
+        <v>135751490</v>
       </c>
       <c r="B18" t="n">
-        <v>104628</v>
+        <v>79813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,34 +2430,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>6430</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>724542</v>
+        <v>724851</v>
       </c>
       <c r="R18" t="n">
-        <v>6645741</v>
+        <v>6645576</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,12 +2484,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2450,16 +2525,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157198</t>
+          <t>https://artportalen.se/Sighting/135751490</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127157709</v>
+        <v>135751496</v>
       </c>
       <c r="B19" t="n">
-        <v>104628</v>
+        <v>79813</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2467,34 +2542,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>6430</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>724476</v>
+        <v>724821</v>
       </c>
       <c r="R19" t="n">
-        <v>6645815</v>
+        <v>6645639</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,12 +2596,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2552,16 +2637,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157709</t>
+          <t>https://artportalen.se/Sighting/135751496</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127156623</v>
+        <v>135751510</v>
       </c>
       <c r="B20" t="n">
-        <v>101326</v>
+        <v>79813</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,34 +2654,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>6430</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>724500</v>
+        <v>724816</v>
       </c>
       <c r="R20" t="n">
-        <v>6645668</v>
+        <v>6645381</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,12 +2708,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2654,16 +2749,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127156623</t>
+          <t>https://artportalen.se/Sighting/135751510</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127156873</v>
+        <v>135821829</v>
       </c>
       <c r="B21" t="n">
-        <v>101326</v>
+        <v>79813</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,34 +2766,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6430</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>724534</v>
+        <v>724703</v>
       </c>
       <c r="R21" t="n">
-        <v>6645685</v>
+        <v>6645341</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,12 +2820,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2756,16 +2851,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127156873</t>
+          <t>https://artportalen.se/Sighting/135821829</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127157120</v>
+        <v>135820121</v>
       </c>
       <c r="B22" t="n">
-        <v>101326</v>
+        <v>79821</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,34 +2868,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>6431</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>724542</v>
+        <v>724757</v>
       </c>
       <c r="R22" t="n">
-        <v>6645741</v>
+        <v>6645305</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,12 +2922,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2858,16 +2953,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157120</t>
+          <t>https://artportalen.se/Sighting/135820121</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127157323</v>
+        <v>135821643</v>
       </c>
       <c r="B23" t="n">
-        <v>101326</v>
+        <v>80481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2875,34 +2970,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>6457</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>724570</v>
+        <v>724719</v>
       </c>
       <c r="R23" t="n">
-        <v>6645756</v>
+        <v>6645325</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,12 +3024,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2960,51 +3055,54 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157323</t>
+          <t>https://artportalen.se/Sighting/135821643</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127157427</v>
+        <v>135819579</v>
       </c>
       <c r="B24" t="n">
-        <v>101326</v>
+        <v>80556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>724605</v>
+        <v>724742</v>
       </c>
       <c r="R24" t="n">
-        <v>6645716</v>
+        <v>6645308</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,12 +3129,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Välmående stora och små bålar utspridda på en ek. Även bål på gran som står precis intill.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3045,6 +3148,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3062,51 +3166,51 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157427</t>
+          <t>https://artportalen.se/Sighting/135819579</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127157668</v>
+        <v>135820104</v>
       </c>
       <c r="B25" t="n">
-        <v>101326</v>
+        <v>80556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>724479</v>
+        <v>724757</v>
       </c>
       <c r="R25" t="n">
-        <v>6645800</v>
+        <v>6645305</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,12 +3237,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Välmående stora och små bålar på en ek.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3164,51 +3273,58 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157668</t>
+          <t>https://artportalen.se/Sighting/135820104</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127157212</v>
+        <v>135820396</v>
       </c>
       <c r="B26" t="n">
-        <v>101228</v>
+        <v>80556</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>724542</v>
+        <v>724749</v>
       </c>
       <c r="R26" t="n">
-        <v>6645741</v>
+        <v>6645315</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,12 +3351,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt på två ekar intill varandra. Bålar med apothecier på båda träden.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3249,6 +3370,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3266,51 +3388,54 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127157212</t>
+          <t>https://artportalen.se/Sighting/135820396</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127157952</v>
+        <v>135821119</v>
       </c>
       <c r="B27" t="n">
-        <v>101228</v>
+        <v>80556</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ytterstycket, Upl</t>
+          <t>Finnala, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>724463</v>
+        <v>724751</v>
       </c>
       <c r="R27" t="n">
-        <v>6645828</v>
+        <v>6645330</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,12 +3462,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Flera små och större bålar på tre senvuxna aspar. En "medelstor" bål på död stående ek.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3351,6 +3481,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3368,7 +3499,5459 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135821119</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135821600</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>724719</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6645325</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera stora och små bålar på en ek.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135821600</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135821957</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80567</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>724697</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6645352</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135821957</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135820852</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>724774</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6645318</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135820852</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135751465</v>
+      </c>
+      <c r="B31" t="n">
+        <v>111561</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>724881</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6645460</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751465</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135751500</v>
+      </c>
+      <c r="B32" t="n">
+        <v>111561</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>724809</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6645642</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751500</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127157363</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>724582</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6645761</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157363</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127157657</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>724479</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6645800</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157657</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>69478687</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99218</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>400 m O om Utanå, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>724694</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6646089</v>
+      </c>
+      <c r="S35" t="n">
+        <v>100</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2000-12-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69478687</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127157276</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>724549</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6645754</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157276</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135751503</v>
+      </c>
+      <c r="B37" t="n">
+        <v>108292</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>724808</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6645661</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751503</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>69718341</v>
+      </c>
+      <c r="B38" t="n">
+        <v>109947</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>40 m V om torpet Strömmen, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>724876</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6645413</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>1998-12-31</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>6 blomstänglar och ca 20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>I gräsvegetation på kanten av en gammal traktorväg</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69718341</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>69478692</v>
+      </c>
+      <c r="B39" t="n">
+        <v>104880</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220460</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tandrot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cardamine bulbifera</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Finnalnäset, Utanå, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>724694</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6646089</v>
+      </c>
+      <c r="S39" t="n">
+        <v>100</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2000-12-31</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69478692</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135751470</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106981</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>724904</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6645471</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Grov.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751470</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127156619</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>724500</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6645668</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127156619</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127157474</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>724605</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6645716</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157474</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127157730</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>724476</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6645815</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157730</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135751466</v>
+      </c>
+      <c r="B44" t="n">
+        <v>106323</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>724881</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6645460</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751466</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135751505</v>
+      </c>
+      <c r="B45" t="n">
+        <v>106323</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>724815</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6645657</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751505</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135821774</v>
+      </c>
+      <c r="B46" t="n">
+        <v>106323</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>724703</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6645332</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135821774</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127156732</v>
+      </c>
+      <c r="B47" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>724500</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6645668</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127156732</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127156885</v>
+      </c>
+      <c r="B48" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>724534</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6645685</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127156885</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127157320</v>
+      </c>
+      <c r="B49" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>724570</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6645756</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157320</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127157449</v>
+      </c>
+      <c r="B50" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>724605</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6645716</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157449</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127157962</v>
+      </c>
+      <c r="B51" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>724463</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6645828</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157962</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135751459</v>
+      </c>
+      <c r="B52" t="n">
+        <v>102399</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>724851</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6645435</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751459</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135751483</v>
+      </c>
+      <c r="B53" t="n">
+        <v>102399</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>724917</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6645460</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751483</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135751501</v>
+      </c>
+      <c r="B54" t="n">
+        <v>102399</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>724808</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6645644</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751501</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135751507</v>
+      </c>
+      <c r="B55" t="n">
+        <v>102399</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>724811</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6645385</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751507</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135821023</v>
+      </c>
+      <c r="B56" t="n">
+        <v>102399</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>724755</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6645325</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135821023</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135821757</v>
+      </c>
+      <c r="B57" t="n">
+        <v>102399</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>724703</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6645332</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135821757</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127157198</v>
+      </c>
+      <c r="B58" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>724542</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6645741</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157198</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127157709</v>
+      </c>
+      <c r="B59" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>724476</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6645815</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157709</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127156623</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>724500</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6645668</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127156623</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127156873</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>724534</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6645685</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127156873</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127157120</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>724542</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6645741</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157120</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127157323</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>724570</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6645756</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157323</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127157427</v>
+      </c>
+      <c r="B64" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>724605</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6645716</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157427</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127157668</v>
+      </c>
+      <c r="B65" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>724479</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6645800</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157668</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135751452</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>724791</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6645421</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751452</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135751460</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>724851</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6645435</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751460</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135751468</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>724881</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6645460</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751468</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135751494</v>
+      </c>
+      <c r="B69" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>724822</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6645586</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751494</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135751499</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>724821</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6645639</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751499</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135751513</v>
+      </c>
+      <c r="B71" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>724824</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6645368</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751513</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135821033</v>
+      </c>
+      <c r="B72" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>724755</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6645325</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135821033</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135821746</v>
+      </c>
+      <c r="B73" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>724703</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6645332</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135821746</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127157212</v>
+      </c>
+      <c r="B74" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>724542</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6645741</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127157212</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127157952</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Ytterstycket, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>724463</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6645828</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/127157952</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135751455</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>724796</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6645409</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751455</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135751493</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>724822</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6645586</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751493</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135821989</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Finnala, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>724697</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6645352</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135821989</t>
         </is>
       </c>
     </row>
@@ -3400,6 +8983,57 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>96182</v>
+        <v>96184</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>96577</v>
+        <v>96579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>135751450</v>
       </c>
       <c r="B4" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>135751458</v>
       </c>
       <c r="B5" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135751491</v>
       </c>
       <c r="B6" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>135751508</v>
       </c>
       <c r="B7" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>135751448</v>
       </c>
       <c r="B8" t="n">
-        <v>92105</v>
+        <v>92107</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>135751465</v>
       </c>
       <c r="B31" t="n">
-        <v>111561</v>
+        <v>111563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>135751500</v>
       </c>
       <c r="B32" t="n">
-        <v>111561</v>
+        <v>111563</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>135751503</v>
       </c>
       <c r="B37" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135751470</v>
       </c>
       <c r="B40" t="n">
-        <v>106981</v>
+        <v>106983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>135751466</v>
       </c>
       <c r="B44" t="n">
-        <v>106323</v>
+        <v>106325</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>135751505</v>
       </c>
       <c r="B45" t="n">
-        <v>106323</v>
+        <v>106325</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>135821774</v>
       </c>
       <c r="B46" t="n">
-        <v>106323</v>
+        <v>106325</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135751459</v>
       </c>
       <c r="B52" t="n">
-        <v>102399</v>
+        <v>102401</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>135751483</v>
       </c>
       <c r="B53" t="n">
-        <v>102399</v>
+        <v>102401</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>135751501</v>
       </c>
       <c r="B54" t="n">
-        <v>102399</v>
+        <v>102401</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>135751507</v>
       </c>
       <c r="B55" t="n">
-        <v>102399</v>
+        <v>102401</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135821023</v>
       </c>
       <c r="B56" t="n">
-        <v>102399</v>
+        <v>102401</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>135821757</v>
       </c>
       <c r="B57" t="n">
-        <v>102399</v>
+        <v>102401</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>135751452</v>
       </c>
       <c r="B66" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>135751460</v>
       </c>
       <c r="B67" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>135751468</v>
       </c>
       <c r="B68" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135751494</v>
       </c>
       <c r="B69" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135751499</v>
       </c>
       <c r="B70" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>135751513</v>
       </c>
       <c r="B71" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>135821033</v>
       </c>
       <c r="B72" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>135821746</v>
       </c>
       <c r="B73" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>135751455</v>
       </c>
       <c r="B76" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135751493</v>
       </c>
       <c r="B77" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>135821989</v>
       </c>
       <c r="B78" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>96184</v>
+        <v>96201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>96579</v>
+        <v>96596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>135751450</v>
       </c>
       <c r="B4" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>135751458</v>
       </c>
       <c r="B5" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135751491</v>
       </c>
       <c r="B6" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>135751508</v>
       </c>
       <c r="B7" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>135751448</v>
       </c>
       <c r="B8" t="n">
-        <v>92107</v>
+        <v>92121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>135751469</v>
       </c>
       <c r="B9" t="n">
-        <v>75414</v>
+        <v>75416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>135751495</v>
       </c>
       <c r="B10" t="n">
-        <v>75414</v>
+        <v>75416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>135820804</v>
       </c>
       <c r="B11" t="n">
-        <v>75400</v>
+        <v>75402</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>135751453</v>
       </c>
       <c r="B14" t="n">
-        <v>79813</v>
+        <v>79815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>135751461</v>
       </c>
       <c r="B15" t="n">
-        <v>79813</v>
+        <v>79815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>135751463</v>
       </c>
       <c r="B16" t="n">
-        <v>79813</v>
+        <v>79815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>135751471</v>
       </c>
       <c r="B17" t="n">
-        <v>79813</v>
+        <v>79815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>135751490</v>
       </c>
       <c r="B18" t="n">
-        <v>79813</v>
+        <v>79815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135751496</v>
       </c>
       <c r="B19" t="n">
-        <v>79813</v>
+        <v>79815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135751510</v>
       </c>
       <c r="B20" t="n">
-        <v>79813</v>
+        <v>79815</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135821829</v>
       </c>
       <c r="B21" t="n">
-        <v>79813</v>
+        <v>79815</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>135820121</v>
       </c>
       <c r="B22" t="n">
-        <v>79821</v>
+        <v>79823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135821643</v>
       </c>
       <c r="B23" t="n">
-        <v>80481</v>
+        <v>80483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>135819579</v>
       </c>
       <c r="B24" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>135820104</v>
       </c>
       <c r="B25" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135820396</v>
       </c>
       <c r="B26" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>135821119</v>
       </c>
       <c r="B27" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135821600</v>
       </c>
       <c r="B28" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135821957</v>
       </c>
       <c r="B29" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>135820852</v>
       </c>
       <c r="B30" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>135751465</v>
       </c>
       <c r="B31" t="n">
-        <v>111563</v>
+        <v>111586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>135751500</v>
       </c>
       <c r="B32" t="n">
-        <v>111563</v>
+        <v>111586</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>135751503</v>
       </c>
       <c r="B37" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135751470</v>
       </c>
       <c r="B40" t="n">
-        <v>106983</v>
+        <v>107003</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>135751466</v>
       </c>
       <c r="B44" t="n">
-        <v>106325</v>
+        <v>106345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>135751505</v>
       </c>
       <c r="B45" t="n">
-        <v>106325</v>
+        <v>106345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>135821774</v>
       </c>
       <c r="B46" t="n">
-        <v>106325</v>
+        <v>106345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135751459</v>
       </c>
       <c r="B52" t="n">
-        <v>102401</v>
+        <v>102418</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>135751483</v>
       </c>
       <c r="B53" t="n">
-        <v>102401</v>
+        <v>102418</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>135751501</v>
       </c>
       <c r="B54" t="n">
-        <v>102401</v>
+        <v>102418</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>135751507</v>
       </c>
       <c r="B55" t="n">
-        <v>102401</v>
+        <v>102418</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135821023</v>
       </c>
       <c r="B56" t="n">
-        <v>102401</v>
+        <v>102418</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>135821757</v>
       </c>
       <c r="B57" t="n">
-        <v>102401</v>
+        <v>102418</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>135751452</v>
       </c>
       <c r="B66" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>135751460</v>
       </c>
       <c r="B67" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>135751468</v>
       </c>
       <c r="B68" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135751494</v>
       </c>
       <c r="B69" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135751499</v>
       </c>
       <c r="B70" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>135751513</v>
       </c>
       <c r="B71" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>135821033</v>
       </c>
       <c r="B72" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>135821746</v>
       </c>
       <c r="B73" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>135751455</v>
       </c>
       <c r="B76" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135751493</v>
       </c>
       <c r="B77" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>135821989</v>
       </c>
       <c r="B78" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>96201</v>
+        <v>96202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>96596</v>
+        <v>96597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>135751450</v>
       </c>
       <c r="B4" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>135751458</v>
       </c>
       <c r="B5" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135751491</v>
       </c>
       <c r="B6" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>135751508</v>
       </c>
       <c r="B7" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>135751448</v>
       </c>
       <c r="B8" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>135751469</v>
       </c>
       <c r="B9" t="n">
-        <v>75416</v>
+        <v>75417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>135751495</v>
       </c>
       <c r="B10" t="n">
-        <v>75416</v>
+        <v>75417</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>135820804</v>
       </c>
       <c r="B11" t="n">
-        <v>75402</v>
+        <v>75403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>135751453</v>
       </c>
       <c r="B14" t="n">
-        <v>79815</v>
+        <v>79816</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>135751461</v>
       </c>
       <c r="B15" t="n">
-        <v>79815</v>
+        <v>79816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>135751463</v>
       </c>
       <c r="B16" t="n">
-        <v>79815</v>
+        <v>79816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>135751471</v>
       </c>
       <c r="B17" t="n">
-        <v>79815</v>
+        <v>79816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>135751490</v>
       </c>
       <c r="B18" t="n">
-        <v>79815</v>
+        <v>79816</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135751496</v>
       </c>
       <c r="B19" t="n">
-        <v>79815</v>
+        <v>79816</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135751510</v>
       </c>
       <c r="B20" t="n">
-        <v>79815</v>
+        <v>79816</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135821829</v>
       </c>
       <c r="B21" t="n">
-        <v>79815</v>
+        <v>79816</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>135820121</v>
       </c>
       <c r="B22" t="n">
-        <v>79823</v>
+        <v>79824</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135821643</v>
       </c>
       <c r="B23" t="n">
-        <v>80483</v>
+        <v>80484</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>135819579</v>
       </c>
       <c r="B24" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>135820104</v>
       </c>
       <c r="B25" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135820396</v>
       </c>
       <c r="B26" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>135821119</v>
       </c>
       <c r="B27" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135821600</v>
       </c>
       <c r="B28" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135821957</v>
       </c>
       <c r="B29" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>135751465</v>
       </c>
       <c r="B31" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>135751500</v>
       </c>
       <c r="B32" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>135751503</v>
       </c>
       <c r="B37" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135751470</v>
       </c>
       <c r="B40" t="n">
-        <v>107003</v>
+        <v>107005</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>135751466</v>
       </c>
       <c r="B44" t="n">
-        <v>106345</v>
+        <v>106347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>135751505</v>
       </c>
       <c r="B45" t="n">
-        <v>106345</v>
+        <v>106347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>135821774</v>
       </c>
       <c r="B46" t="n">
-        <v>106345</v>
+        <v>106347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135751459</v>
       </c>
       <c r="B52" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>135751483</v>
       </c>
       <c r="B53" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>135751501</v>
       </c>
       <c r="B54" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>135751507</v>
       </c>
       <c r="B55" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135821023</v>
       </c>
       <c r="B56" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>135821757</v>
       </c>
       <c r="B57" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>135751452</v>
       </c>
       <c r="B66" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>135751460</v>
       </c>
       <c r="B67" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>135751468</v>
       </c>
       <c r="B68" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135751494</v>
       </c>
       <c r="B69" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135751499</v>
       </c>
       <c r="B70" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>135751513</v>
       </c>
       <c r="B71" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>135821033</v>
       </c>
       <c r="B72" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>135821746</v>
       </c>
       <c r="B73" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>135751455</v>
       </c>
       <c r="B76" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135751493</v>
       </c>
       <c r="B77" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>135821989</v>
       </c>
       <c r="B78" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>96202</v>
+        <v>96203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>96597</v>
+        <v>96598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>135751450</v>
       </c>
       <c r="B4" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>135751458</v>
       </c>
       <c r="B5" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135751491</v>
       </c>
       <c r="B6" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>135751508</v>
       </c>
       <c r="B7" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>135751448</v>
       </c>
       <c r="B8" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>135751465</v>
       </c>
       <c r="B31" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>135751500</v>
       </c>
       <c r="B32" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>135751503</v>
       </c>
       <c r="B37" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135751470</v>
       </c>
       <c r="B40" t="n">
-        <v>107005</v>
+        <v>107006</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>135751466</v>
       </c>
       <c r="B44" t="n">
-        <v>106347</v>
+        <v>106348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>135751505</v>
       </c>
       <c r="B45" t="n">
-        <v>106347</v>
+        <v>106348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>135821774</v>
       </c>
       <c r="B46" t="n">
-        <v>106347</v>
+        <v>106348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135751459</v>
       </c>
       <c r="B52" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>135751483</v>
       </c>
       <c r="B53" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>135751501</v>
       </c>
       <c r="B54" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>135751507</v>
       </c>
       <c r="B55" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135821023</v>
       </c>
       <c r="B56" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>135821757</v>
       </c>
       <c r="B57" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>135751452</v>
       </c>
       <c r="B66" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>135751460</v>
       </c>
       <c r="B67" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>135751468</v>
       </c>
       <c r="B68" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135751494</v>
       </c>
       <c r="B69" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135751499</v>
       </c>
       <c r="B70" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>135751513</v>
       </c>
       <c r="B71" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>135821033</v>
       </c>
       <c r="B72" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>135821746</v>
       </c>
       <c r="B73" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>135751455</v>
       </c>
       <c r="B76" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135751493</v>
       </c>
       <c r="B77" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>135821989</v>
       </c>
       <c r="B78" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>96203</v>
+        <v>96204</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>96598</v>
+        <v>96599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>135751450</v>
       </c>
       <c r="B4" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>135751458</v>
       </c>
       <c r="B5" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135751491</v>
       </c>
       <c r="B6" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>135751508</v>
       </c>
       <c r="B7" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>135751448</v>
       </c>
       <c r="B8" t="n">
-        <v>92123</v>
+        <v>92124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>135751469</v>
       </c>
       <c r="B9" t="n">
-        <v>75417</v>
+        <v>75418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>135751495</v>
       </c>
       <c r="B10" t="n">
-        <v>75417</v>
+        <v>75418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>135820804</v>
       </c>
       <c r="B11" t="n">
-        <v>75403</v>
+        <v>75404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>135751453</v>
       </c>
       <c r="B14" t="n">
-        <v>79816</v>
+        <v>79817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>135751461</v>
       </c>
       <c r="B15" t="n">
-        <v>79816</v>
+        <v>79817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>135751463</v>
       </c>
       <c r="B16" t="n">
-        <v>79816</v>
+        <v>79817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>135751471</v>
       </c>
       <c r="B17" t="n">
-        <v>79816</v>
+        <v>79817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>135751490</v>
       </c>
       <c r="B18" t="n">
-        <v>79816</v>
+        <v>79817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135751496</v>
       </c>
       <c r="B19" t="n">
-        <v>79816</v>
+        <v>79817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135751510</v>
       </c>
       <c r="B20" t="n">
-        <v>79816</v>
+        <v>79817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135821829</v>
       </c>
       <c r="B21" t="n">
-        <v>79816</v>
+        <v>79817</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>135820121</v>
       </c>
       <c r="B22" t="n">
-        <v>79824</v>
+        <v>79825</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135821643</v>
       </c>
       <c r="B23" t="n">
-        <v>80484</v>
+        <v>80485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>135819579</v>
       </c>
       <c r="B24" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>135820104</v>
       </c>
       <c r="B25" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135820396</v>
       </c>
       <c r="B26" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>135821119</v>
       </c>
       <c r="B27" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135821600</v>
       </c>
       <c r="B28" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135821957</v>
       </c>
       <c r="B29" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>135820852</v>
       </c>
       <c r="B30" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>135751465</v>
       </c>
       <c r="B31" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>135751500</v>
       </c>
       <c r="B32" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>135751503</v>
       </c>
       <c r="B37" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135751470</v>
       </c>
       <c r="B40" t="n">
-        <v>107006</v>
+        <v>107007</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>135751466</v>
       </c>
       <c r="B44" t="n">
-        <v>106348</v>
+        <v>106349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>135751505</v>
       </c>
       <c r="B45" t="n">
-        <v>106348</v>
+        <v>106349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>135821774</v>
       </c>
       <c r="B46" t="n">
-        <v>106348</v>
+        <v>106349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135751459</v>
       </c>
       <c r="B52" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>135751483</v>
       </c>
       <c r="B53" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>135751501</v>
       </c>
       <c r="B54" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>135751507</v>
       </c>
       <c r="B55" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135821023</v>
       </c>
       <c r="B56" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>135821757</v>
       </c>
       <c r="B57" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>135751452</v>
       </c>
       <c r="B66" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>135751460</v>
       </c>
       <c r="B67" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>135751468</v>
       </c>
       <c r="B68" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135751494</v>
       </c>
       <c r="B69" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135751499</v>
       </c>
       <c r="B70" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>135751513</v>
       </c>
       <c r="B71" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>135821033</v>
       </c>
       <c r="B72" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>135821746</v>
       </c>
       <c r="B73" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>135751455</v>
       </c>
       <c r="B76" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135751493</v>
       </c>
       <c r="B77" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>135821989</v>
       </c>
       <c r="B78" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>96204</v>
+        <v>96210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>135751450</v>
       </c>
       <c r="B4" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>135751458</v>
       </c>
       <c r="B5" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135751491</v>
       </c>
       <c r="B6" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>135751508</v>
       </c>
       <c r="B7" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>135751448</v>
       </c>
       <c r="B8" t="n">
-        <v>92124</v>
+        <v>92130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>135751469</v>
       </c>
       <c r="B9" t="n">
-        <v>75418</v>
+        <v>75422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>135751495</v>
       </c>
       <c r="B10" t="n">
-        <v>75418</v>
+        <v>75422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>135820804</v>
       </c>
       <c r="B11" t="n">
-        <v>75404</v>
+        <v>75408</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>135751453</v>
       </c>
       <c r="B14" t="n">
-        <v>79817</v>
+        <v>79821</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>135751461</v>
       </c>
       <c r="B15" t="n">
-        <v>79817</v>
+        <v>79821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>135751463</v>
       </c>
       <c r="B16" t="n">
-        <v>79817</v>
+        <v>79821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>135751471</v>
       </c>
       <c r="B17" t="n">
-        <v>79817</v>
+        <v>79821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>135751490</v>
       </c>
       <c r="B18" t="n">
-        <v>79817</v>
+        <v>79821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135751496</v>
       </c>
       <c r="B19" t="n">
-        <v>79817</v>
+        <v>79821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135751510</v>
       </c>
       <c r="B20" t="n">
-        <v>79817</v>
+        <v>79821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135821829</v>
       </c>
       <c r="B21" t="n">
-        <v>79817</v>
+        <v>79821</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>135820121</v>
       </c>
       <c r="B22" t="n">
-        <v>79825</v>
+        <v>79829</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135821643</v>
       </c>
       <c r="B23" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>135819579</v>
       </c>
       <c r="B24" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>135820104</v>
       </c>
       <c r="B25" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135820396</v>
       </c>
       <c r="B26" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>135821119</v>
       </c>
       <c r="B27" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135821600</v>
       </c>
       <c r="B28" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135821957</v>
       </c>
       <c r="B29" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>135820852</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>135751465</v>
       </c>
       <c r="B31" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>135751500</v>
       </c>
       <c r="B32" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>135751503</v>
       </c>
       <c r="B37" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135751470</v>
       </c>
       <c r="B40" t="n">
-        <v>107007</v>
+        <v>107013</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>135751466</v>
       </c>
       <c r="B44" t="n">
-        <v>106349</v>
+        <v>106355</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>135751505</v>
       </c>
       <c r="B45" t="n">
-        <v>106349</v>
+        <v>106355</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>135821774</v>
       </c>
       <c r="B46" t="n">
-        <v>106349</v>
+        <v>106355</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135751459</v>
       </c>
       <c r="B52" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>135751483</v>
       </c>
       <c r="B53" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>135751501</v>
       </c>
       <c r="B54" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>135751507</v>
       </c>
       <c r="B55" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135821023</v>
       </c>
       <c r="B56" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>135821757</v>
       </c>
       <c r="B57" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>135751452</v>
       </c>
       <c r="B66" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>135751460</v>
       </c>
       <c r="B67" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>135751468</v>
       </c>
       <c r="B68" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135751494</v>
       </c>
       <c r="B69" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135751499</v>
       </c>
       <c r="B70" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>135751513</v>
       </c>
       <c r="B71" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>135821033</v>
       </c>
       <c r="B72" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>135821746</v>
       </c>
       <c r="B73" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>135751455</v>
       </c>
       <c r="B76" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135751493</v>
       </c>
       <c r="B77" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>135821989</v>
       </c>
       <c r="B78" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>96605</v>
+        <v>96606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>135751450</v>
       </c>
       <c r="B4" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>135751458</v>
       </c>
       <c r="B5" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135751491</v>
       </c>
       <c r="B6" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>135751508</v>
       </c>
       <c r="B7" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>135751448</v>
       </c>
       <c r="B8" t="n">
-        <v>92130</v>
+        <v>92131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>135751469</v>
       </c>
       <c r="B9" t="n">
-        <v>75422</v>
+        <v>75423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>135751495</v>
       </c>
       <c r="B10" t="n">
-        <v>75422</v>
+        <v>75423</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>135820804</v>
       </c>
       <c r="B11" t="n">
-        <v>75408</v>
+        <v>75409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>135751453</v>
       </c>
       <c r="B14" t="n">
-        <v>79821</v>
+        <v>79822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>135751461</v>
       </c>
       <c r="B15" t="n">
-        <v>79821</v>
+        <v>79822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>135751463</v>
       </c>
       <c r="B16" t="n">
-        <v>79821</v>
+        <v>79822</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>135751471</v>
       </c>
       <c r="B17" t="n">
-        <v>79821</v>
+        <v>79822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>135751490</v>
       </c>
       <c r="B18" t="n">
-        <v>79821</v>
+        <v>79822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135751496</v>
       </c>
       <c r="B19" t="n">
-        <v>79821</v>
+        <v>79822</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135751510</v>
       </c>
       <c r="B20" t="n">
-        <v>79821</v>
+        <v>79822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135821829</v>
       </c>
       <c r="B21" t="n">
-        <v>79821</v>
+        <v>79822</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>135820121</v>
       </c>
       <c r="B22" t="n">
-        <v>79829</v>
+        <v>79830</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135821643</v>
       </c>
       <c r="B23" t="n">
-        <v>80489</v>
+        <v>80490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>135819579</v>
       </c>
       <c r="B24" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>135820104</v>
       </c>
       <c r="B25" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135820396</v>
       </c>
       <c r="B26" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>135821119</v>
       </c>
       <c r="B27" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135821600</v>
       </c>
       <c r="B28" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135821957</v>
       </c>
       <c r="B29" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>135820852</v>
       </c>
       <c r="B30" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>135751465</v>
       </c>
       <c r="B31" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>135751500</v>
       </c>
       <c r="B32" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>135751503</v>
       </c>
       <c r="B37" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135751470</v>
       </c>
       <c r="B40" t="n">
-        <v>107013</v>
+        <v>107014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>135751466</v>
       </c>
       <c r="B44" t="n">
-        <v>106355</v>
+        <v>106356</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>135751505</v>
       </c>
       <c r="B45" t="n">
-        <v>106355</v>
+        <v>106356</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>135821774</v>
       </c>
       <c r="B46" t="n">
-        <v>106355</v>
+        <v>106356</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135751459</v>
       </c>
       <c r="B52" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>135751483</v>
       </c>
       <c r="B53" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>135751501</v>
       </c>
       <c r="B54" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>135751507</v>
       </c>
       <c r="B55" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135821023</v>
       </c>
       <c r="B56" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>135821757</v>
       </c>
       <c r="B57" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>135751452</v>
       </c>
       <c r="B66" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>135751460</v>
       </c>
       <c r="B67" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>135751468</v>
       </c>
       <c r="B68" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135751494</v>
       </c>
       <c r="B69" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135751499</v>
       </c>
       <c r="B70" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>135751513</v>
       </c>
       <c r="B71" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>135821033</v>
       </c>
       <c r="B72" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>135821746</v>
       </c>
       <c r="B73" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>135751455</v>
       </c>
       <c r="B76" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135751493</v>
       </c>
       <c r="B77" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>135821989</v>
       </c>
       <c r="B78" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>96211</v>
+        <v>96222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>96606</v>
+        <v>96617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>135751450</v>
       </c>
       <c r="B4" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>135751458</v>
       </c>
       <c r="B5" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135751491</v>
       </c>
       <c r="B6" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>135751508</v>
       </c>
       <c r="B7" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>135751448</v>
       </c>
       <c r="B8" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>135751469</v>
       </c>
       <c r="B9" t="n">
-        <v>75423</v>
+        <v>75427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>135751495</v>
       </c>
       <c r="B10" t="n">
-        <v>75423</v>
+        <v>75427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>135820804</v>
       </c>
       <c r="B11" t="n">
-        <v>75409</v>
+        <v>75413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>135751453</v>
       </c>
       <c r="B14" t="n">
-        <v>79822</v>
+        <v>79826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>135751461</v>
       </c>
       <c r="B15" t="n">
-        <v>79822</v>
+        <v>79826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>135751463</v>
       </c>
       <c r="B16" t="n">
-        <v>79822</v>
+        <v>79826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>135751471</v>
       </c>
       <c r="B17" t="n">
-        <v>79822</v>
+        <v>79826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>135751490</v>
       </c>
       <c r="B18" t="n">
-        <v>79822</v>
+        <v>79826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135751496</v>
       </c>
       <c r="B19" t="n">
-        <v>79822</v>
+        <v>79826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135751510</v>
       </c>
       <c r="B20" t="n">
-        <v>79822</v>
+        <v>79826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135821829</v>
       </c>
       <c r="B21" t="n">
-        <v>79822</v>
+        <v>79826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>135820121</v>
       </c>
       <c r="B22" t="n">
-        <v>79830</v>
+        <v>79834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135821643</v>
       </c>
       <c r="B23" t="n">
-        <v>80490</v>
+        <v>80494</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>135819579</v>
       </c>
       <c r="B24" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>135820104</v>
       </c>
       <c r="B25" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135820396</v>
       </c>
       <c r="B26" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>135821119</v>
       </c>
       <c r="B27" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135821600</v>
       </c>
       <c r="B28" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135821957</v>
       </c>
       <c r="B29" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>135751465</v>
       </c>
       <c r="B31" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>135751500</v>
       </c>
       <c r="B32" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>135751503</v>
       </c>
       <c r="B37" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135751470</v>
       </c>
       <c r="B40" t="n">
-        <v>107014</v>
+        <v>107025</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>135751466</v>
       </c>
       <c r="B44" t="n">
-        <v>106356</v>
+        <v>106367</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>135751505</v>
       </c>
       <c r="B45" t="n">
-        <v>106356</v>
+        <v>106367</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>135821774</v>
       </c>
       <c r="B46" t="n">
-        <v>106356</v>
+        <v>106367</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135751459</v>
       </c>
       <c r="B52" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>135751483</v>
       </c>
       <c r="B53" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>135751501</v>
       </c>
       <c r="B54" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>135751507</v>
       </c>
       <c r="B55" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135821023</v>
       </c>
       <c r="B56" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>135821757</v>
       </c>
       <c r="B57" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>135751452</v>
       </c>
       <c r="B66" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>135751460</v>
       </c>
       <c r="B67" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>135751468</v>
       </c>
       <c r="B68" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135751494</v>
       </c>
       <c r="B69" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135751499</v>
       </c>
       <c r="B70" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>135751513</v>
       </c>
       <c r="B71" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>135821033</v>
       </c>
       <c r="B72" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>135821746</v>
       </c>
       <c r="B73" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>135751455</v>
       </c>
       <c r="B76" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135751493</v>
       </c>
       <c r="B77" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>135821989</v>
       </c>
       <c r="B78" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>96222</v>
+        <v>96235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>96617</v>
+        <v>96630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>135751450</v>
       </c>
       <c r="B4" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>135751458</v>
       </c>
       <c r="B5" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135751491</v>
       </c>
       <c r="B6" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>135751508</v>
       </c>
       <c r="B7" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>135751448</v>
       </c>
       <c r="B8" t="n">
-        <v>92137</v>
+        <v>92144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>135751469</v>
       </c>
       <c r="B9" t="n">
-        <v>75427</v>
+        <v>75433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>135751495</v>
       </c>
       <c r="B10" t="n">
-        <v>75427</v>
+        <v>75433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>135820804</v>
       </c>
       <c r="B11" t="n">
-        <v>75413</v>
+        <v>75419</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>135751453</v>
       </c>
       <c r="B14" t="n">
-        <v>79826</v>
+        <v>79832</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>135751461</v>
       </c>
       <c r="B15" t="n">
-        <v>79826</v>
+        <v>79832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>135751463</v>
       </c>
       <c r="B16" t="n">
-        <v>79826</v>
+        <v>79832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>135751471</v>
       </c>
       <c r="B17" t="n">
-        <v>79826</v>
+        <v>79832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>135751490</v>
       </c>
       <c r="B18" t="n">
-        <v>79826</v>
+        <v>79832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135751496</v>
       </c>
       <c r="B19" t="n">
-        <v>79826</v>
+        <v>79832</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135751510</v>
       </c>
       <c r="B20" t="n">
-        <v>79826</v>
+        <v>79832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135821829</v>
       </c>
       <c r="B21" t="n">
-        <v>79826</v>
+        <v>79832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>135820121</v>
       </c>
       <c r="B22" t="n">
-        <v>79834</v>
+        <v>79840</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135821643</v>
       </c>
       <c r="B23" t="n">
-        <v>80494</v>
+        <v>80500</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>135819579</v>
       </c>
       <c r="B24" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>135820104</v>
       </c>
       <c r="B25" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135820396</v>
       </c>
       <c r="B26" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>135821119</v>
       </c>
       <c r="B27" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135821600</v>
       </c>
       <c r="B28" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135821957</v>
       </c>
       <c r="B29" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>135820852</v>
       </c>
       <c r="B30" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>135751465</v>
       </c>
       <c r="B31" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>135751500</v>
       </c>
       <c r="B32" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>135751503</v>
       </c>
       <c r="B37" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135751470</v>
       </c>
       <c r="B40" t="n">
-        <v>107025</v>
+        <v>107038</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>135751466</v>
       </c>
       <c r="B44" t="n">
-        <v>106367</v>
+        <v>106380</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>135751505</v>
       </c>
       <c r="B45" t="n">
-        <v>106367</v>
+        <v>106380</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>135821774</v>
       </c>
       <c r="B46" t="n">
-        <v>106367</v>
+        <v>106380</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135751459</v>
       </c>
       <c r="B52" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>135751483</v>
       </c>
       <c r="B53" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>135751501</v>
       </c>
       <c r="B54" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>135751507</v>
       </c>
       <c r="B55" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135821023</v>
       </c>
       <c r="B56" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>135821757</v>
       </c>
       <c r="B57" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>135751452</v>
       </c>
       <c r="B66" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>135751460</v>
       </c>
       <c r="B67" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>135751468</v>
       </c>
       <c r="B68" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135751494</v>
       </c>
       <c r="B69" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135751499</v>
       </c>
       <c r="B70" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>135751513</v>
       </c>
       <c r="B71" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>135821033</v>
       </c>
       <c r="B72" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>135821746</v>
       </c>
       <c r="B73" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>135751455</v>
       </c>
       <c r="B76" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135751493</v>
       </c>
       <c r="B77" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>135821989</v>
       </c>
       <c r="B78" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>96235</v>
+        <v>96236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>135821774</v>
       </c>
       <c r="B46" t="n">
-        <v>106380</v>
+        <v>106381</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135821023</v>
       </c>
       <c r="B56" t="n">
-        <v>102453</v>
+        <v>102454</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>135821757</v>
       </c>
       <c r="B57" t="n">
-        <v>102453</v>
+        <v>102454</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>135821033</v>
       </c>
       <c r="B72" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>135821746</v>
       </c>
       <c r="B73" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>135821989</v>
       </c>
       <c r="B78" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 50326-2024 artfynd.xlsx
+++ b/artfynd/A 50326-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135822036</v>
       </c>
       <c r="B2" t="n">
-        <v>96236</v>
+        <v>96249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>135821503</v>
       </c>
       <c r="B3" t="n">
-        <v>96631</v>
+        <v>96644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>135820804</v>
       </c>
       <c r="B11" t="n">
-        <v>75419</v>
+        <v>75432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135821829</v>
       </c>
       <c r="B21" t="n">
-        <v>79832</v>
+        <v>79845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>135820121</v>
       </c>
       <c r="B22" t="n">
-        <v>79840</v>
+        <v>79853</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135821643</v>
       </c>
       <c r="B23" t="n">
-        <v>80500</v>
+        <v>80513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>135819579</v>
       </c>
       <c r="B24" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>135820104</v>
       </c>
       <c r="B25" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135820396</v>
       </c>
       <c r="B26" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>135821119</v>
       </c>
       <c r="B27" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>135821600</v>
       </c>
       <c r="B28" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135821957</v>
       </c>
       <c r="B29" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>135820852</v>
       </c>
       <c r="B30" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>135821774</v>
       </c>
       <c r="B46" t="n">
-        <v>106381</v>
+        <v>106394</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135821023</v>
       </c>
       <c r="B56" t="n">
-        <v>102454</v>
+        <v>102467</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>135821757</v>
       </c>
       <c r="B57" t="n">
-        <v>102454</v>
+        <v>102467</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>135821033</v>
       </c>
       <c r="B72" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>135821746</v>
       </c>
       <c r="B73" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>135821989</v>
       </c>
       <c r="B78" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
